--- a/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
+++ b/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\ArduinoIDE\_Project\SelfDrivingCar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494AD5FE-67AA-4FD8-9DCC-0299AA8EB55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C86B171-EB35-46F5-BEBB-6A2E9C90EED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
   <si>
     <t>(0,0)</t>
   </si>
@@ -322,6 +322,10 @@
   </si>
   <si>
     <t>寫程式陣列用：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電線長度(final)：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -589,21 +593,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -632,6 +622,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>291914</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>35297</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>542184</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>35299</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A543A6B-1B4A-43FA-B158-F37EEC1D4C6A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7702364" y="8550647"/>
+          <a:ext cx="3764995" cy="2305052"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -931,15 +987,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Z50"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.875" customWidth="1"/>
     <col min="2" max="6" width="5.625" customWidth="1"/>
     <col min="7" max="7" width="5.875" customWidth="1"/>
     <col min="8" max="9" width="5.625" customWidth="1"/>
-    <col min="10" max="10" width="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.375" customWidth="1"/>
     <col min="11" max="16" width="5.625" customWidth="1"/>
+    <col min="18" max="18" width="6.75" customWidth="1"/>
+    <col min="19" max="25" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1675,7 +1733,7 @@
         <v>{1,1,1,0,0,1}</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:25">
       <c r="B18" s="4" t="s">
         <v>0</v>
       </c>
@@ -1683,7 +1741,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:25">
       <c r="B19" s="6" t="s">
         <v>1</v>
       </c>
@@ -1691,7 +1749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:25">
       <c r="B20" s="16" t="s">
         <v>10</v>
       </c>
@@ -1699,7 +1757,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:25">
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
@@ -1707,15 +1765,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:25">
       <c r="B28" t="s">
         <v>12</v>
       </c>
       <c r="K28" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="T28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="B29" s="10"/>
       <c r="C29" s="11">
         <v>150</v>
@@ -1732,24 +1793,42 @@
       <c r="G29" s="12"/>
       <c r="K29" s="10"/>
       <c r="L29" s="11">
-        <f>C29+20</f>
-        <v>170</v>
+        <f t="shared" ref="L29:L31" si="10">C29-15</f>
+        <v>135</v>
       </c>
       <c r="M29" s="11">
-        <f t="shared" ref="M29:O32" si="10">D29+20</f>
-        <v>200</v>
+        <f t="shared" ref="M29:M31" si="11">D29-15</f>
+        <v>165</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" si="10"/>
-        <v>230</v>
+        <f t="shared" ref="N29:N31" si="12">E29-15</f>
+        <v>195</v>
       </c>
       <c r="O29" s="11">
-        <f t="shared" si="10"/>
-        <v>260</v>
+        <f t="shared" ref="O29:O31" si="13">F29-15</f>
+        <v>225</v>
       </c>
       <c r="P29" s="12"/>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="T29" s="10"/>
+      <c r="U29" s="11">
+        <f>L29+20</f>
+        <v>155</v>
+      </c>
+      <c r="V29" s="11">
+        <f t="shared" ref="V29:V32" si="14">M29+20</f>
+        <v>185</v>
+      </c>
+      <c r="W29" s="11">
+        <f t="shared" ref="W29:W32" si="15">N29+20</f>
+        <v>215</v>
+      </c>
+      <c r="X29" s="11">
+        <f t="shared" ref="X29:X32" si="16">O29+20</f>
+        <v>245</v>
+      </c>
+      <c r="Y29" s="12"/>
+    </row>
+    <row r="30" spans="1:25">
       <c r="B30" s="13"/>
       <c r="C30" s="11">
         <v>120</v>
@@ -1766,24 +1845,42 @@
       <c r="G30" s="13"/>
       <c r="K30" s="13"/>
       <c r="L30" s="11">
-        <f t="shared" ref="L30:L32" si="11">C30+20</f>
-        <v>140</v>
+        <f t="shared" si="10"/>
+        <v>105</v>
       </c>
       <c r="M30" s="11">
-        <f t="shared" si="10"/>
-        <v>170</v>
+        <f t="shared" si="11"/>
+        <v>135</v>
       </c>
       <c r="N30" s="11">
-        <f t="shared" si="10"/>
-        <v>200</v>
+        <f t="shared" si="12"/>
+        <v>165</v>
       </c>
       <c r="O30" s="11">
-        <f t="shared" si="10"/>
-        <v>230</v>
+        <f t="shared" si="13"/>
+        <v>195</v>
       </c>
       <c r="P30" s="13"/>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="T30" s="13"/>
+      <c r="U30" s="11">
+        <f t="shared" ref="U30:U32" si="17">L30+20</f>
+        <v>125</v>
+      </c>
+      <c r="V30" s="11">
+        <f t="shared" si="14"/>
+        <v>155</v>
+      </c>
+      <c r="W30" s="11">
+        <f t="shared" si="15"/>
+        <v>185</v>
+      </c>
+      <c r="X30" s="11">
+        <f t="shared" si="16"/>
+        <v>215</v>
+      </c>
+      <c r="Y30" s="13"/>
+    </row>
+    <row r="31" spans="1:25">
       <c r="B31" s="11"/>
       <c r="C31" s="11">
         <v>90</v>
@@ -1800,24 +1897,42 @@
       <c r="G31" s="13"/>
       <c r="K31" s="11"/>
       <c r="L31" s="11">
+        <f t="shared" si="10"/>
+        <v>75</v>
+      </c>
+      <c r="M31" s="11">
         <f t="shared" si="11"/>
-        <v>110</v>
-      </c>
-      <c r="M31" s="11">
-        <f t="shared" si="10"/>
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="N31" s="11">
-        <f t="shared" si="10"/>
-        <v>170</v>
+        <f t="shared" si="12"/>
+        <v>135</v>
       </c>
       <c r="O31" s="11">
-        <f t="shared" si="10"/>
-        <v>200</v>
+        <f t="shared" si="13"/>
+        <v>165</v>
       </c>
       <c r="P31" s="13"/>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="T31" s="11"/>
+      <c r="U31" s="11">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="V31" s="11">
+        <f t="shared" si="14"/>
+        <v>125</v>
+      </c>
+      <c r="W31" s="11">
+        <f t="shared" si="15"/>
+        <v>155</v>
+      </c>
+      <c r="X31" s="11">
+        <f t="shared" si="16"/>
+        <v>185</v>
+      </c>
+      <c r="Y31" s="13"/>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="17" t="s">
         <v>11</v>
       </c>
@@ -1840,38 +1955,59 @@
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="11">
-        <f t="shared" si="11"/>
-        <v>80</v>
+        <f>C32-15</f>
+        <v>45</v>
       </c>
       <c r="M32" s="11">
-        <f t="shared" si="10"/>
-        <v>110</v>
+        <f t="shared" ref="M32:O32" si="18">D32-15</f>
+        <v>75</v>
       </c>
       <c r="N32" s="11">
-        <f t="shared" si="10"/>
-        <v>140</v>
+        <f t="shared" si="18"/>
+        <v>105</v>
       </c>
       <c r="O32" s="11">
-        <f t="shared" si="10"/>
-        <v>170</v>
+        <f t="shared" si="18"/>
+        <v>135</v>
       </c>
       <c r="P32" s="14"/>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="S32" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11">
+        <f t="shared" si="17"/>
+        <v>65</v>
+      </c>
+      <c r="V32" s="11">
+        <f t="shared" si="14"/>
+        <v>95</v>
+      </c>
+      <c r="W32" s="11">
+        <f t="shared" si="15"/>
+        <v>125</v>
+      </c>
+      <c r="X32" s="11">
+        <f t="shared" si="16"/>
+        <v>155</v>
+      </c>
+      <c r="Y32" s="14"/>
+    </row>
+    <row r="33" spans="1:26">
       <c r="C33">
         <f>SUM(C29:C32)</f>
         <v>420</v>
       </c>
       <c r="D33">
-        <f t="shared" ref="D33:F33" si="12">SUM(D29:D32)</f>
+        <f t="shared" ref="D33:F33" si="19">SUM(D29:D32)</f>
         <v>540</v>
       </c>
       <c r="E33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>660</v>
       </c>
       <c r="F33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>780</v>
       </c>
       <c r="G33">
@@ -1880,26 +2016,46 @@
       </c>
       <c r="L33">
         <f>SUM(L29:L32)</f>
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="M33">
-        <f t="shared" ref="M33" si="13">SUM(M29:M32)</f>
-        <v>620</v>
+        <f t="shared" ref="M33" si="20">SUM(M29:M32)</f>
+        <v>480</v>
       </c>
       <c r="N33">
-        <f t="shared" ref="N33" si="14">SUM(N29:N32)</f>
-        <v>740</v>
+        <f t="shared" ref="N33" si="21">SUM(N29:N32)</f>
+        <v>600</v>
       </c>
       <c r="O33">
-        <f t="shared" ref="O33" si="15">SUM(O29:O32)</f>
-        <v>860</v>
+        <f t="shared" ref="O33" si="22">SUM(O29:O32)</f>
+        <v>720</v>
       </c>
       <c r="P33">
         <f>SUM(L33:O33)</f>
-        <v>2720</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17">
+        <v>2160</v>
+      </c>
+      <c r="U33">
+        <f>SUM(U29:U32)</f>
+        <v>440</v>
+      </c>
+      <c r="V33">
+        <f t="shared" ref="V33:X33" si="23">SUM(V29:V32)</f>
+        <v>560</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="23"/>
+        <v>680</v>
+      </c>
+      <c r="X33">
+        <f t="shared" si="23"/>
+        <v>800</v>
+      </c>
+      <c r="Y33">
+        <f>SUM(U33:X33)</f>
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26">
       <c r="G34" s="18">
         <f>G33/100</f>
         <v>24</v>
@@ -1909,28 +2065,42 @@
       </c>
       <c r="P34" s="18">
         <f>P33/100</f>
-        <v>27.2</v>
+        <v>21.6</v>
       </c>
       <c r="Q34" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="35" spans="1:17">
+      <c r="Y34" s="18">
+        <f>Y33/100</f>
+        <v>24.8</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26">
       <c r="G35" s="18">
         <f>G34*3</f>
         <v>72</v>
       </c>
       <c r="P35" s="18">
         <f>P34*3</f>
-        <v>81.599999999999994</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
+        <v>64.800000000000011</v>
+      </c>
+      <c r="T35" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y35" s="18">
+        <f>Y34*3</f>
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26">
       <c r="B37" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:26">
       <c r="B38">
         <v>0</v>
       </c>
@@ -1950,7 +2120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:26">
       <c r="A39">
         <v>0</v>
       </c>
@@ -1973,7 +2143,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:26">
       <c r="A40">
         <v>1</v>
       </c>
@@ -1996,7 +2166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:26">
       <c r="A41">
         <v>2</v>
       </c>
@@ -2019,7 +2189,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:26">
       <c r="A42">
         <v>3</v>
       </c>
@@ -2042,13 +2212,13 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:26">
       <c r="J45" s="19"/>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:26">
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:26">
       <c r="J48" s="20"/>
     </row>
     <row r="49" spans="10:10">
@@ -2060,27 +2230,18 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="J13:O16">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:F16">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>K13=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29:F32">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>K29=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L29:O32">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>T29=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
+++ b/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\ArduinoIDE\_Project\SelfDrivingCar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C86B171-EB35-46F5-BEBB-6A2E9C90EED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14FFCC5-28AE-496E-8783-4CC5CA3C7C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
   <si>
     <t>(0,0)</t>
   </si>
@@ -326,6 +326,10 @@
   </si>
   <si>
     <t>電線長度(final)：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(0,5)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1743,7 +1747,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="B19" s="6" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
         <v>2</v>

--- a/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
+++ b/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\ArduinoIDE\_Project\SelfDrivingCar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14FFCC5-28AE-496E-8783-4CC5CA3C7C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D973D9C-A235-43AE-AC97-BEF99F5493DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,34 +88,6 @@
   </si>
   <si>
     <t>*3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>安裝磁簧管的格子(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>綠色</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -330,6 +302,34 @@
   </si>
   <si>
     <t>(0,5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>安裝磁簧管的格子(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="4" tint="0.39997558519241921"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>藍色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -372,14 +372,6 @@
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="9" tint="-0.249977111117893"/>
-      <name val="新細明體"/>
-      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -431,8 +423,16 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="4" tint="0.39997558519241921"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -481,6 +481,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -511,7 +517,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -575,22 +581,28 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -670,7 +682,7 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm rot="10800000">
           <a:off x="7702364" y="8550647"/>
           <a:ext cx="3764995" cy="2305052"/>
         </a:xfrm>
@@ -1539,10 +1551,11 @@
         <f t="shared" ref="F13:F16" si="7">"("&amp;$A13&amp;","&amp;M$1&amp;")"</f>
         <v>(0,4)</v>
       </c>
-      <c r="G13" s="12" t="str">
+      <c r="G13" s="11" t="str">
         <f t="shared" si="4"/>
         <v>(0,5)</v>
       </c>
+      <c r="H13" s="17"/>
       <c r="I13">
         <v>0</v>
       </c>
@@ -1687,7 +1700,7 @@
       <c r="A16" s="17">
         <v>3</v>
       </c>
-      <c r="B16" s="11" t="str">
+      <c r="B16" s="12" t="str">
         <f t="shared" si="4"/>
         <v>(3,0)</v>
       </c>
@@ -1737,7 +1750,7 @@
         <v>{1,1,1,0,0,1}</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:26">
       <c r="B18" s="4" t="s">
         <v>0</v>
       </c>
@@ -1745,23 +1758,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:26">
       <c r="B19" s="6" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:26">
       <c r="B20" s="16" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:26">
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
@@ -1769,7 +1782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:26">
       <c r="B28" t="s">
         <v>12</v>
       </c>
@@ -1777,10 +1790,10 @@
         <v>12</v>
       </c>
       <c r="T28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26">
       <c r="B29" s="10"/>
       <c r="C29" s="11">
         <v>150</v>
@@ -1794,7 +1807,10 @@
       <c r="F29" s="11">
         <v>240</v>
       </c>
-      <c r="G29" s="12"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="17" t="s">
+        <v>11</v>
+      </c>
       <c r="K29" s="10"/>
       <c r="L29" s="11">
         <f t="shared" ref="L29:L31" si="10">C29-15</f>
@@ -1812,7 +1828,10 @@
         <f t="shared" ref="O29:O31" si="13">F29-15</f>
         <v>225</v>
       </c>
-      <c r="P29" s="12"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="17" t="s">
+        <v>11</v>
+      </c>
       <c r="T29" s="10"/>
       <c r="U29" s="11">
         <f>L29+20</f>
@@ -1830,9 +1849,12 @@
         <f t="shared" ref="X29:X32" si="16">O29+20</f>
         <v>245</v>
       </c>
-      <c r="Y29" s="12"/>
-    </row>
-    <row r="30" spans="1:25">
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26">
       <c r="B30" s="13"/>
       <c r="C30" s="11">
         <v>120</v>
@@ -1884,7 +1906,7 @@
       </c>
       <c r="Y30" s="13"/>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:26">
       <c r="B31" s="11"/>
       <c r="C31" s="11">
         <v>90</v>
@@ -1936,11 +1958,9 @@
       </c>
       <c r="Y31" s="13"/>
     </row>
-    <row r="32" spans="1:25">
-      <c r="A32" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="11"/>
+    <row r="32" spans="1:26">
+      <c r="A32" s="27"/>
+      <c r="B32" s="12"/>
       <c r="C32" s="11">
         <v>60</v>
       </c>
@@ -1954,10 +1974,8 @@
         <v>150</v>
       </c>
       <c r="G32" s="14"/>
-      <c r="J32" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K32" s="11"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="12"/>
       <c r="L32" s="11">
         <f>C32-15</f>
         <v>45</v>
@@ -1975,10 +1993,8 @@
         <v>135</v>
       </c>
       <c r="P32" s="14"/>
-      <c r="S32" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="T32" s="11"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="12"/>
       <c r="U32" s="11">
         <f t="shared" si="17"/>
         <v>65</v>
@@ -2101,7 +2117,7 @@
     </row>
     <row r="37" spans="1:26">
       <c r="B37" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:26">
@@ -2131,20 +2147,20 @@
       <c r="B39" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="E39" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="F39" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="G39" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:26">
@@ -2152,22 +2168,22 @@
         <v>1</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="D40" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="E40" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="F40" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="G40" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:26">
@@ -2177,20 +2193,20 @@
       <c r="B41" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="E41" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="F41" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="G41" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:26">
@@ -2198,22 +2214,22 @@
         <v>3</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="D42" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="E42" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="G42" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:26">
@@ -2262,16 +2278,16 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J1" s="19"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="24">
         <v>22.636458299926499</v>
@@ -2283,7 +2299,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="24">
         <v>120.30257035839</v>
@@ -2295,7 +2311,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="24">
         <v>22.631900522567602</v>
@@ -2307,7 +2323,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="24">
         <v>120.310326561398</v>
@@ -2482,10 +2498,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -2494,7 +2510,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -2517,12 +2533,12 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="2:7">
       <c r="B18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="28.5">

--- a/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
+++ b/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\ArduinoIDE\_Project\SelfDrivingCar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D973D9C-A235-43AE-AC97-BEF99F5493DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CF00FF-2105-4074-BC73-942C54328134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1697,7 +1697,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="39.950000000000003" customHeight="1">
-      <c r="A16" s="17">
+      <c r="A16" s="27">
         <v>3</v>
       </c>
       <c r="B16" s="12" t="str">

--- a/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
+++ b/ArduinoIDE/_Project/SelfDrivingCar/maps.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\ArduinoIDE\_Project\SelfDrivingCar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\Maker\ArduinoSample\ArduinoIDE\_Project\SelfDrivingCar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CF00FF-2105-4074-BC73-942C54328134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="GPS" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="53">
   <si>
     <t>(0,0)</t>
   </si>
@@ -332,18 +331,27 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>物流</t>
+  </si>
+  <si>
+    <t>充電</t>
+  </si>
+  <si>
+    <t>客戶</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="General&quot;m&quot;"/>
     <numFmt numFmtId="177" formatCode="0.0000000000000"/>
     <numFmt numFmtId="178" formatCode="0.000000000000000"/>
     <numFmt numFmtId="179" formatCode="0.000000000000000_ "/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1002,21 +1010,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z50"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.875" customWidth="1"/>
-    <col min="2" max="6" width="5.625" customWidth="1"/>
-    <col min="7" max="7" width="5.875" customWidth="1"/>
-    <col min="8" max="9" width="5.625" customWidth="1"/>
-    <col min="10" max="10" width="5.375" customWidth="1"/>
-    <col min="11" max="16" width="5.625" customWidth="1"/>
-    <col min="18" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="25" width="5.625" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" customWidth="1"/>
+    <col min="2" max="6" width="5.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.88671875" customWidth="1"/>
+    <col min="8" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="5.33203125" customWidth="1"/>
+    <col min="11" max="16" width="5.6640625" customWidth="1"/>
+    <col min="18" max="18" width="6.77734375" customWidth="1"/>
+    <col min="19" max="25" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>0</v>
       </c>
@@ -1057,7 +1065,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1117,7 +1125,7 @@
         <v>(0,7)</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1177,7 +1185,7 @@
         <v>(1,7)</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1237,7 +1245,7 @@
         <v>(2,7)</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1297,7 +1305,7 @@
         <v>(3,7)</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1357,7 +1365,7 @@
         <v>(4,7)</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="H7">
         <v>5</v>
       </c>
@@ -1394,7 +1402,7 @@
         <v>(5,7)</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="H8">
         <v>6</v>
       </c>
@@ -1431,7 +1439,7 @@
         <v>(6,7)</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="H9">
         <v>7</v>
       </c>
@@ -1468,7 +1476,7 @@
         <v>(7,7)</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
@@ -1478,7 +1486,7 @@
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
@@ -1489,7 +1497,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>0</v>
       </c>
@@ -1527,7 +1535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="39.950000000000003" customHeight="1">
+    <row r="13" spans="1:17" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0</v>
       </c>
@@ -1582,7 +1590,7 @@
         <v>{1,1,0,1,1,1},</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="39.950000000000003" customHeight="1">
+    <row r="14" spans="1:17" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -1636,7 +1644,7 @@
         <v>{1,0,0,1,0,1},</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="39.950000000000003" customHeight="1">
+    <row r="15" spans="1:17" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1696,7 +1704,7 @@
         <v>{1,0,1,1,0,1},</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="39.950000000000003" customHeight="1">
+    <row r="16" spans="1:17" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="27">
         <v>3</v>
       </c>
@@ -1750,7 +1758,7 @@
         <v>{1,1,1,0,0,1}</v>
       </c>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>0</v>
       </c>
@@ -1758,7 +1766,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
@@ -1766,7 +1774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B20" s="16" t="s">
         <v>48</v>
       </c>
@@ -1774,7 +1782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
@@ -1782,7 +1790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>12</v>
       </c>
@@ -1793,7 +1801,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B29" s="10"/>
       <c r="C29" s="11">
         <v>150</v>
@@ -1854,7 +1862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B30" s="13"/>
       <c r="C30" s="11">
         <v>120</v>
@@ -1906,7 +1914,7 @@
       </c>
       <c r="Y30" s="13"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B31" s="11"/>
       <c r="C31" s="11">
         <v>90</v>
@@ -1958,7 +1966,7 @@
       </c>
       <c r="Y31" s="13"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32" s="27"/>
       <c r="B32" s="12"/>
       <c r="C32" s="11">
@@ -2013,7 +2021,7 @@
       </c>
       <c r="Y32" s="14"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C33">
         <f>SUM(C29:C32)</f>
         <v>420</v>
@@ -2075,7 +2083,7 @@
         <v>2480</v>
       </c>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="G34" s="18">
         <f>G33/100</f>
         <v>24</v>
@@ -2098,7 +2106,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="G35" s="18">
         <f>G34*3</f>
         <v>72</v>
@@ -2115,12 +2123,12 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>0</v>
       </c>
@@ -2140,7 +2148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0</v>
       </c>
@@ -2163,7 +2171,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1</v>
       </c>
@@ -2186,7 +2194,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>2</v>
       </c>
@@ -2209,7 +2217,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -2232,19 +2240,107 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:26">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B44" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J45" s="19"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B47" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>52</v>
+      </c>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="10:10">
+    <row r="49" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="10:10">
+    <row r="50" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J50" s="20"/>
     </row>
   </sheetData>
@@ -2266,17 +2362,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27292DF4-BBF0-48FD-AF98-588E17F9C7F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" customWidth="1"/>
     <col min="2" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.77734375" customWidth="1"/>
+    <col min="10" max="10" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>45</v>
       </c>
@@ -2285,7 +2381,7 @@
       </c>
       <c r="J1" s="19"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>36</v>
       </c>
@@ -2297,7 +2393,7 @@
       </c>
       <c r="J2" s="19"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>38</v>
       </c>
@@ -2309,7 +2405,7 @@
       </c>
       <c r="J3" s="19"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>37</v>
       </c>
@@ -2321,7 +2417,7 @@
       </c>
       <c r="J4" s="19"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
         <v>39</v>
       </c>
@@ -2333,10 +2429,10 @@
       </c>
       <c r="J5" s="19"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J6" s="19"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>0</v>
       </c>
@@ -2356,7 +2452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.5">
+    <row r="8" spans="1:10" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0</v>
       </c>
@@ -2391,7 +2487,7 @@
 120.310326561398</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28.5" customHeight="1">
+    <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -2426,7 +2522,7 @@
 120.310326561398</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.5" customHeight="1">
+    <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2461,7 +2557,7 @@
 120.310326561398</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28.5" customHeight="1">
+    <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>3</v>
       </c>
@@ -2496,7 +2592,7 @@
 120.310326561398</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="26" t="s">
         <v>42</v>
       </c>
@@ -2508,7 +2604,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="26" t="s">
         <v>43</v>
       </c>
@@ -2518,7 +2614,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -2526,7 +2622,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2536,12 +2632,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="28.5">
+    <row r="19" spans="2:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="B19" s="21" t="str">
         <f>$B$2&amp;","&amp;$B$3</f>
         <v>22.6364582999265,120.30257035839</v>
@@ -2567,7 +2663,7 @@
         <v>22.6364582999265,120.310326561398</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="28.5">
+    <row r="20" spans="2:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="B20" s="22" t="str">
         <f>($B$2+($B$4-$B$2)/3)&amp;","&amp;$B$3</f>
         <v>22.6349390408069,120.30257035839</v>
@@ -2593,7 +2689,7 @@
         <v>22.6349390408069,120.310326561398</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="28.5">
+    <row r="21" spans="2:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="B21" s="22" t="str">
         <f>($B$2+2*($B$4-$B$2)/3)&amp;","&amp;$B$3</f>
         <v>22.6334197816872,120.30257035839</v>
@@ -2619,7 +2715,7 @@
         <v>22.6334197816872,120.310326561398</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="28.5">
+    <row r="22" spans="2:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="str">
         <f>($B$2+3*($B$4-$B$2)/3)&amp;","&amp;$B$3</f>
         <v>22.6319005225676,120.30257035839</v>
